--- a/Day_8_Date_Time_Functions.xlsx
+++ b/Day_8_Date_Time_Functions.xlsx
@@ -8,13 +8,21 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\30_Days_Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8D7C143-7F44-49E3-878D-600A585DBC66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C93438CD-FD3A-4236-A5E9-33BD1BD8922A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{77431055-04CD-4D7C-9741-704A5462B3EA}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{77431055-04CD-4D7C-9741-704A5462B3EA}"/>
   </bookViews>
   <sheets>
-    <sheet name="Data" sheetId="2" r:id="rId1"/>
+    <sheet name="Data" sheetId="5" r:id="rId1"/>
+    <sheet name="Date" sheetId="6" r:id="rId2"/>
+    <sheet name="Time" sheetId="7" r:id="rId3"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId4"/>
+  </externalReferences>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Time!$A$1:$H$21</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -33,30 +41,8 @@
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
-</file>
-
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="470" uniqueCount="96">
   <si>
     <t>Applicant ID</t>
   </si>
@@ -343,7 +329,7 @@
     <t>AID0123567</t>
   </si>
   <si>
-    <t>hour</t>
+    <t>Count</t>
   </si>
 </sst>
 </file>
@@ -531,7 +517,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -549,6 +535,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -600,12 +587,16 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr lang="en-IN"/>
-              <a:t>Job</a:t>
+              <a:rPr lang="en-US"/>
+              <a:t>Application</a:t>
             </a:r>
             <a:r>
-              <a:rPr lang="en-IN" baseline="0"/>
-              <a:t> posting per hour</a:t>
+              <a:rPr lang="en-US" baseline="0"/>
+              <a:t> </a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Count by Hour</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -649,6 +640,17 @@
         <c:ser>
           <c:idx val="0"/>
           <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Time!$R$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Count</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
           <c:spPr>
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -661,9 +663,9 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:numRef>
-              <c:f>Data!$AA$2:$AA$25</c:f>
+              <c:f>Time!$Q$3:$Q$26</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>@</c:formatCode>
                 <c:ptCount val="24"/>
                 <c:pt idx="0">
                   <c:v>1</c:v>
@@ -742,7 +744,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Data!$AB$2:$AB$25</c:f>
+              <c:f>Time!$R$3:$R$26</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="24"/>
@@ -806,12 +808,24 @@
                 <c:pt idx="19">
                   <c:v>0</c:v>
                 </c:pt>
+                <c:pt idx="20">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>0</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-4E19-4217-B013-58D703FF246F}"/>
+              <c16:uniqueId val="{00000000-5470-4154-8F35-778CAC01612F}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -825,17 +839,72 @@
         </c:dLbls>
         <c:gapWidth val="219"/>
         <c:overlap val="-27"/>
-        <c:axId val="1571306800"/>
-        <c:axId val="1571320240"/>
+        <c:axId val="562951488"/>
+        <c:axId val="562952448"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="1571306800"/>
+        <c:axId val="562951488"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Hour</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="@" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -872,7 +941,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1571320240"/>
+        <c:crossAx val="562952448"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -880,7 +949,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="1571320240"/>
+        <c:axId val="562952448"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -931,7 +1000,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1571306800"/>
+        <c:crossAx val="562951488"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1527,27 +1596,29 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>29</xdr:col>
-      <xdr:colOff>297180</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>72390</xdr:rowOff>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>123824</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>4762</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>39</xdr:col>
-      <xdr:colOff>83820</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>83820</xdr:rowOff>
+      <xdr:col>29</xdr:col>
+      <xdr:colOff>19049</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>142875</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
         <xdr:cNvPr id="2" name="Chart 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{17544206-B0C4-C593-F744-6714264CF165}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A48051D5-2FAB-4869-A803-D466F0D1BC42}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
-        <xdr:cNvGraphicFramePr/>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="0" y="0"/>
@@ -1562,6 +1633,225 @@
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
+</file>
+
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Data"/>
+      <sheetName val="Date"/>
+      <sheetName val="Time"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="2">
+        <row r="2">
+          <cell r="R2" t="str">
+            <v>Count</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="Q3">
+            <v>1</v>
+          </cell>
+          <cell r="R3">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="Q4">
+            <v>2</v>
+          </cell>
+          <cell r="R4">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="Q5">
+            <v>3</v>
+          </cell>
+          <cell r="R5">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="Q6">
+            <v>4</v>
+          </cell>
+          <cell r="R6">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="Q7">
+            <v>5</v>
+          </cell>
+          <cell r="R7">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="8">
+          <cell r="Q8">
+            <v>6</v>
+          </cell>
+          <cell r="R8">
+            <v>1</v>
+          </cell>
+        </row>
+        <row r="9">
+          <cell r="Q9">
+            <v>7</v>
+          </cell>
+          <cell r="R9">
+            <v>3</v>
+          </cell>
+        </row>
+        <row r="10">
+          <cell r="Q10">
+            <v>8</v>
+          </cell>
+          <cell r="R10">
+            <v>1</v>
+          </cell>
+        </row>
+        <row r="11">
+          <cell r="Q11">
+            <v>9</v>
+          </cell>
+          <cell r="R11">
+            <v>1</v>
+          </cell>
+        </row>
+        <row r="12">
+          <cell r="Q12">
+            <v>10</v>
+          </cell>
+          <cell r="R12">
+            <v>1</v>
+          </cell>
+        </row>
+        <row r="13">
+          <cell r="Q13">
+            <v>11</v>
+          </cell>
+          <cell r="R13">
+            <v>1</v>
+          </cell>
+        </row>
+        <row r="14">
+          <cell r="Q14">
+            <v>12</v>
+          </cell>
+          <cell r="R14">
+            <v>1</v>
+          </cell>
+        </row>
+        <row r="15">
+          <cell r="Q15">
+            <v>13</v>
+          </cell>
+          <cell r="R15">
+            <v>1</v>
+          </cell>
+        </row>
+        <row r="16">
+          <cell r="Q16">
+            <v>14</v>
+          </cell>
+          <cell r="R16">
+            <v>1</v>
+          </cell>
+        </row>
+        <row r="17">
+          <cell r="Q17">
+            <v>15</v>
+          </cell>
+          <cell r="R17">
+            <v>1</v>
+          </cell>
+        </row>
+        <row r="18">
+          <cell r="Q18">
+            <v>16</v>
+          </cell>
+          <cell r="R18">
+            <v>1</v>
+          </cell>
+        </row>
+        <row r="19">
+          <cell r="Q19">
+            <v>17</v>
+          </cell>
+          <cell r="R19">
+            <v>7</v>
+          </cell>
+        </row>
+        <row r="20">
+          <cell r="Q20">
+            <v>18</v>
+          </cell>
+          <cell r="R20">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="21">
+          <cell r="Q21">
+            <v>19</v>
+          </cell>
+          <cell r="R21">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="22">
+          <cell r="Q22">
+            <v>20</v>
+          </cell>
+          <cell r="R22">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="23">
+          <cell r="Q23">
+            <v>21</v>
+          </cell>
+          <cell r="R23">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="24">
+          <cell r="Q24">
+            <v>22</v>
+          </cell>
+          <cell r="R24">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="25">
+          <cell r="Q25">
+            <v>23</v>
+          </cell>
+          <cell r="R25">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="26">
+          <cell r="Q26">
+            <v>24</v>
+          </cell>
+          <cell r="R26">
+            <v>0</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1860,23 +2150,21 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A1DA9948-D976-4D41-80A1-C67EE0DE6F6D}">
-  <dimension ref="A1:AB25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1AF5768B-BF5C-4C9C-82F1-27B50C7D1EE3}">
+  <dimension ref="A1:AB21"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17.5546875" customWidth="1"/>
     <col min="2" max="2" width="14.21875" hidden="1" customWidth="1"/>
     <col min="3" max="3" width="27.21875" hidden="1" customWidth="1"/>
     <col min="4" max="4" width="23" style="12" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="26.21875" hidden="1" customWidth="1"/>
-    <col min="6" max="6" width="11" hidden="1" customWidth="1"/>
-    <col min="7" max="7" width="22" hidden="1" customWidth="1"/>
-    <col min="8" max="8" width="40" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="26.21875" customWidth="1"/>
+    <col min="6" max="6" width="11" customWidth="1"/>
+    <col min="7" max="7" width="22" customWidth="1"/>
+    <col min="8" max="8" width="40" customWidth="1"/>
     <col min="10" max="13" width="8.88671875" customWidth="1"/>
     <col min="14" max="14" width="14.21875" customWidth="1"/>
-    <col min="15" max="15" width="8.88671875" customWidth="1"/>
-    <col min="16" max="16" width="9.5546875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="8.88671875" customWidth="1"/>
+    <col min="15" max="17" width="8.88671875" customWidth="1"/>
     <col min="18" max="18" width="16" customWidth="1"/>
     <col min="19" max="23" width="8.88671875" customWidth="1"/>
     <col min="24" max="25" width="14.33203125" customWidth="1"/>
@@ -1942,9 +2230,6 @@
       <c r="Y1" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="Z1" s="6" t="s">
-        <v>95</v>
-      </c>
       <c r="AA1" s="6" t="s">
         <v>18</v>
       </c>
@@ -1975,6 +2260,635 @@
       <c r="H2" s="11" t="s">
         <v>25</v>
       </c>
+      <c r="N2" s="12"/>
+      <c r="P2" s="12"/>
+      <c r="X2" s="13"/>
+    </row>
+    <row r="3" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A3" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="D3" s="10">
+        <v>45055.40662037037</v>
+      </c>
+      <c r="E3" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="F3" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G3" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="H3" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="N3" s="12"/>
+      <c r="X3" s="13"/>
+    </row>
+    <row r="4" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A4" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="D4" s="10">
+        <v>45128.729710648149</v>
+      </c>
+      <c r="E4" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="F4" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="G4" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="H4" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="N4" s="12"/>
+      <c r="X4" s="13"/>
+    </row>
+    <row r="5" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A5" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="D5" s="10">
+        <v>45173.302187499998</v>
+      </c>
+      <c r="E5" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="F5" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="G5" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="H5" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="N5" s="12"/>
+      <c r="X5" s="13"/>
+    </row>
+    <row r="6" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A6" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="B6" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="D6" s="10">
+        <v>45248.70857638889</v>
+      </c>
+      <c r="E6" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="F6" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="G6" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="H6" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="N6" s="12"/>
+      <c r="X6" s="13"/>
+    </row>
+    <row r="7" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A7" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="D7" s="10">
+        <v>45302.531921296293</v>
+      </c>
+      <c r="E7" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="F7" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="G7" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="H7" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="N7" s="12"/>
+      <c r="X7" s="13"/>
+    </row>
+    <row r="8" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A8" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="B8" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="D8" s="10">
+        <v>45354.687881944446</v>
+      </c>
+      <c r="E8" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="F8" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="G8" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="H8" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="N8" s="12"/>
+      <c r="X8" s="13"/>
+    </row>
+    <row r="9" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A9" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="B9" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="D9" s="10">
+        <v>45408.340810185182</v>
+      </c>
+      <c r="E9" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="F9" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="G9" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="H9" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="N9" s="12"/>
+      <c r="X9" s="13"/>
+    </row>
+    <row r="10" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A10" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="B10" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="C10" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="D10" s="10">
+        <v>45458.743333333332</v>
+      </c>
+      <c r="E10" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="F10" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="G10" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="H10" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="N10" s="12"/>
+      <c r="X10" s="13"/>
+    </row>
+    <row r="11" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A11" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="B11" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="C11" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="D11" s="10">
+        <v>45480.608055555553</v>
+      </c>
+      <c r="E11" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="F11" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="G11" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="H11" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="N11" s="12"/>
+      <c r="X11" s="13"/>
+    </row>
+    <row r="12" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A12" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="B12" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="C12" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="D12" s="10">
+        <v>45455.284930555557</v>
+      </c>
+      <c r="E12" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="F12" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="G12" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="H12" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="N12" s="12"/>
+      <c r="X12" s="13"/>
+    </row>
+    <row r="13" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A13" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="B13" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="C13" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="D13" s="10">
+        <v>44951.552141203705</v>
+      </c>
+      <c r="E13" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="F13" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="G13" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="H13" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="N13" s="12"/>
+      <c r="X13" s="13"/>
+    </row>
+    <row r="14" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A14" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="B14" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="C14" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="D14" s="10">
+        <v>45002.490034722221</v>
+      </c>
+      <c r="E14" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="F14" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="G14" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="H14" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="N14" s="12"/>
+      <c r="X14" s="13"/>
+    </row>
+    <row r="15" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A15" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="B15" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="C15" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="D15" s="10">
+        <v>45078.417256944442</v>
+      </c>
+      <c r="E15" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="F15" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="G15" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="H15" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="N15" s="12"/>
+      <c r="X15" s="13"/>
+    </row>
+    <row r="16" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A16" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="B16" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="C16" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="D16" s="10">
+        <v>45168.729328703703</v>
+      </c>
+      <c r="E16" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="F16" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="G16" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="H16" s="11" t="s">
+        <v>84</v>
+      </c>
+      <c r="N16" s="12"/>
+      <c r="X16" s="13"/>
+    </row>
+    <row r="17" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A17" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="B17" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C17" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="D17" s="10">
+        <v>45218.319780092592</v>
+      </c>
+      <c r="E17" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="F17" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G17" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="H17" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="N17" s="12"/>
+      <c r="X17" s="13"/>
+    </row>
+    <row r="18" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A18" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="B18" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="C18" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="D18" s="10">
+        <v>45350.719236111108</v>
+      </c>
+      <c r="E18" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="F18" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="G18" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="H18" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="N18" s="12"/>
+      <c r="X18" s="13"/>
+    </row>
+    <row r="19" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A19" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="B19" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="C19" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="D19" s="10">
+        <v>45418.726354166669</v>
+      </c>
+      <c r="E19" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="F19" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="G19" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="H19" s="11" t="s">
+        <v>92</v>
+      </c>
+      <c r="N19" s="12"/>
+      <c r="X19" s="13"/>
+    </row>
+    <row r="20" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A20" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="B20" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="C20" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="D20" s="10">
+        <v>45496.291701388887</v>
+      </c>
+      <c r="E20" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="F20" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="G20" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="H20" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="N20" s="12"/>
+      <c r="X20" s="13"/>
+    </row>
+    <row r="21" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="B21" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="C21" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="D21" s="15">
+        <v>45422.739884259259</v>
+      </c>
+      <c r="E21" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="F21" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="G21" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="H21" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="N21" s="12"/>
+      <c r="X21" s="13"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E74B1177-9289-45E9-876A-9ED6C288367F}">
+  <dimension ref="A1:R21"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.21875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="23" customWidth="1"/>
+    <col min="5" max="5" width="29.88671875" hidden="1" customWidth="1"/>
+    <col min="6" max="6" width="11" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="22" hidden="1" customWidth="1"/>
+    <col min="8" max="8" width="40" hidden="1" customWidth="1"/>
+    <col min="13" max="13" width="1.88671875" customWidth="1"/>
+    <col min="14" max="14" width="15.88671875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="18" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="K1" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="L1" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="N1" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="P1" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="R1" s="6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A2" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="D2" s="10">
+        <v>44971.640451388892</v>
+      </c>
+      <c r="E2" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="F2" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="G2" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="H2" s="11" t="s">
+        <v>25</v>
+      </c>
       <c r="J2">
         <f>MONTH(D2)</f>
         <v>2</v>
@@ -1993,46 +2907,14 @@
       </c>
       <c r="P2" s="12">
         <f ca="1">TODAY()</f>
-        <v>46095</v>
+        <v>46096</v>
       </c>
       <c r="R2">
-        <f ca="1">DATEDIF(N2,$P$2,"D")</f>
-        <v>1124</v>
-      </c>
-      <c r="T2">
-        <f>HOUR(D2)</f>
-        <v>15</v>
-      </c>
-      <c r="U2">
-        <f>MINUTE(D2)</f>
-        <v>22</v>
-      </c>
-      <c r="V2">
-        <f>SECOND(D2)</f>
-        <v>15</v>
-      </c>
-      <c r="X2" s="13">
-        <f>TIME(T2,U2,V2)</f>
-        <v>0.64045138888888886</v>
-      </c>
-      <c r="Y2" t="str">
-        <f>TEXT(X2,"HH:MM AM/PM")</f>
-        <v>03:22 PM</v>
-      </c>
-      <c r="Z2" cm="1">
-        <f t="array" ref="Z2:Z21">HOUR(Y2:Y21)</f>
-        <v>15</v>
-      </c>
-      <c r="AA2" cm="1">
-        <f t="array" ref="AA2:AA25">_xlfn.SEQUENCE(24,,1)</f>
-        <v>1</v>
-      </c>
-      <c r="AB2">
-        <f>COUNTIF(_xlfn.ANCHORARRAY($Z$2),AA2)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:28" x14ac:dyDescent="0.3">
+        <f ca="1">DATEDIF(D2,$P$2,"D")</f>
+        <v>1125</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A3" s="8" t="s">
         <v>26</v>
       </c>
@@ -2074,41 +2956,11 @@
         <v>45055</v>
       </c>
       <c r="R3">
-        <f t="shared" ref="R3:R22" ca="1" si="4">DATEDIF(N3,$P$2,"D")</f>
-        <v>1040</v>
-      </c>
-      <c r="T3">
-        <f t="shared" ref="T3:T21" si="5">HOUR(D3)</f>
-        <v>9</v>
-      </c>
-      <c r="U3">
-        <f t="shared" ref="U3:U21" si="6">MINUTE(D3)</f>
-        <v>45</v>
-      </c>
-      <c r="V3">
-        <f t="shared" ref="V3:V21" si="7">SECOND(D3)</f>
-        <v>32</v>
-      </c>
-      <c r="X3" s="13">
-        <f t="shared" ref="X3:X21" si="8">TIME(T3,U3,V3)</f>
-        <v>0.40662037037037035</v>
-      </c>
-      <c r="Y3" t="str">
-        <f t="shared" ref="Y3:Y21" si="9">TEXT(X3,"HH:MM AM/PM")</f>
-        <v>09:45 AM</v>
-      </c>
-      <c r="Z3">
-        <v>9</v>
-      </c>
-      <c r="AA3">
-        <v>2</v>
-      </c>
-      <c r="AB3">
-        <f t="shared" ref="AB3:AB21" si="10">COUNTIF(_xlfn.ANCHORARRAY($Z$2),AA3)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:28" x14ac:dyDescent="0.3">
+        <f ca="1">DATEDIF(D3,$P$2,"D")</f>
+        <v>1041</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A4" s="8" t="s">
         <v>33</v>
       </c>
@@ -2150,41 +3002,11 @@
         <v>45128</v>
       </c>
       <c r="R4">
-        <f t="shared" ca="1" si="4"/>
-        <v>967</v>
-      </c>
-      <c r="T4">
-        <f t="shared" si="5"/>
-        <v>17</v>
-      </c>
-      <c r="U4">
-        <f t="shared" si="6"/>
-        <v>30</v>
-      </c>
-      <c r="V4">
-        <f t="shared" si="7"/>
-        <v>47</v>
-      </c>
-      <c r="X4" s="13">
-        <f t="shared" si="8"/>
-        <v>0.72971064814814812</v>
-      </c>
-      <c r="Y4" t="str">
-        <f t="shared" si="9"/>
-        <v>05:30 PM</v>
-      </c>
-      <c r="Z4">
-        <v>17</v>
-      </c>
-      <c r="AA4">
-        <v>3</v>
-      </c>
-      <c r="AB4">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.3">
+        <f t="shared" ref="R4:R21" ca="1" si="4">DATEDIF(D4,$P$2,"D")</f>
+        <v>968</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A5" s="8" t="s">
         <v>39</v>
       </c>
@@ -2227,40 +3049,10 @@
       </c>
       <c r="R5">
         <f t="shared" ca="1" si="4"/>
-        <v>922</v>
-      </c>
-      <c r="T5">
-        <f t="shared" si="5"/>
-        <v>7</v>
-      </c>
-      <c r="U5">
-        <f t="shared" si="6"/>
-        <v>15</v>
-      </c>
-      <c r="V5">
-        <f t="shared" si="7"/>
-        <v>9</v>
-      </c>
-      <c r="X5" s="13">
-        <f t="shared" si="8"/>
-        <v>0.3021875</v>
-      </c>
-      <c r="Y5" t="str">
-        <f t="shared" si="9"/>
-        <v>07:15 AM</v>
-      </c>
-      <c r="Z5">
-        <v>7</v>
-      </c>
-      <c r="AA5">
-        <v>4</v>
-      </c>
-      <c r="AB5">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.3">
+        <v>923</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A6" s="8" t="s">
         <v>40</v>
       </c>
@@ -2303,40 +3095,10 @@
       </c>
       <c r="R6">
         <f t="shared" ca="1" si="4"/>
-        <v>847</v>
-      </c>
-      <c r="T6">
-        <f t="shared" si="5"/>
-        <v>17</v>
-      </c>
-      <c r="U6">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="V6">
-        <f t="shared" si="7"/>
-        <v>21</v>
-      </c>
-      <c r="X6" s="13">
-        <f t="shared" si="8"/>
-        <v>0.70857638888888885</v>
-      </c>
-      <c r="Y6" t="str">
-        <f t="shared" si="9"/>
-        <v>05:00 PM</v>
-      </c>
-      <c r="Z6">
-        <v>17</v>
-      </c>
-      <c r="AA6">
-        <v>5</v>
-      </c>
-      <c r="AB6">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.3">
+        <v>848</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A7" s="8" t="s">
         <v>47</v>
       </c>
@@ -2379,40 +3141,10 @@
       </c>
       <c r="R7">
         <f t="shared" ca="1" si="4"/>
-        <v>793</v>
-      </c>
-      <c r="T7">
-        <f t="shared" si="5"/>
-        <v>12</v>
-      </c>
-      <c r="U7">
-        <f t="shared" si="6"/>
-        <v>45</v>
-      </c>
-      <c r="V7">
-        <f t="shared" si="7"/>
-        <v>58</v>
-      </c>
-      <c r="X7" s="13">
-        <f t="shared" si="8"/>
-        <v>0.53192129629629625</v>
-      </c>
-      <c r="Y7" t="str">
-        <f t="shared" si="9"/>
-        <v>12:45 PM</v>
-      </c>
-      <c r="Z7">
-        <v>12</v>
-      </c>
-      <c r="AA7">
-        <v>6</v>
-      </c>
-      <c r="AB7">
-        <f t="shared" si="10"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.3">
+        <v>794</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A8" s="8" t="s">
         <v>53</v>
       </c>
@@ -2453,42 +3185,13 @@
         <f t="shared" si="3"/>
         <v>45354</v>
       </c>
+      <c r="P8" s="12"/>
       <c r="R8">
         <f t="shared" ca="1" si="4"/>
-        <v>741</v>
-      </c>
-      <c r="T8">
-        <f t="shared" si="5"/>
-        <v>16</v>
-      </c>
-      <c r="U8">
-        <f t="shared" si="6"/>
-        <v>30</v>
-      </c>
-      <c r="V8">
-        <f t="shared" si="7"/>
-        <v>33</v>
-      </c>
-      <c r="X8" s="13">
-        <f t="shared" si="8"/>
-        <v>0.68788194444444439</v>
-      </c>
-      <c r="Y8" t="str">
-        <f t="shared" si="9"/>
-        <v>04:30 PM</v>
-      </c>
-      <c r="Z8">
-        <v>16</v>
-      </c>
-      <c r="AA8">
-        <v>7</v>
-      </c>
-      <c r="AB8">
-        <f t="shared" si="10"/>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:28" x14ac:dyDescent="0.3">
+        <v>742</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A9" s="8" t="s">
         <v>54</v>
       </c>
@@ -2531,40 +3234,10 @@
       </c>
       <c r="R9">
         <f t="shared" ca="1" si="4"/>
-        <v>687</v>
-      </c>
-      <c r="T9">
-        <f t="shared" si="5"/>
-        <v>8</v>
-      </c>
-      <c r="U9">
-        <f t="shared" si="6"/>
-        <v>10</v>
-      </c>
-      <c r="V9">
-        <f t="shared" si="7"/>
-        <v>46</v>
-      </c>
-      <c r="X9" s="13">
-        <f t="shared" si="8"/>
-        <v>0.34081018518518519</v>
-      </c>
-      <c r="Y9" t="str">
-        <f t="shared" si="9"/>
-        <v>08:10 AM</v>
-      </c>
-      <c r="Z9">
-        <v>8</v>
-      </c>
-      <c r="AA9">
-        <v>8</v>
-      </c>
-      <c r="AB9">
-        <f t="shared" si="10"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:28" x14ac:dyDescent="0.3">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A10" s="8" t="s">
         <v>55</v>
       </c>
@@ -2607,40 +3280,10 @@
       </c>
       <c r="R10">
         <f t="shared" ca="1" si="4"/>
-        <v>637</v>
-      </c>
-      <c r="T10">
-        <f t="shared" si="5"/>
-        <v>17</v>
-      </c>
-      <c r="U10">
-        <f t="shared" si="6"/>
-        <v>50</v>
-      </c>
-      <c r="V10">
-        <f t="shared" si="7"/>
-        <v>24</v>
-      </c>
-      <c r="X10" s="13">
-        <f t="shared" si="8"/>
-        <v>0.74333333333333329</v>
-      </c>
-      <c r="Y10" t="str">
-        <f t="shared" si="9"/>
-        <v>05:50 PM</v>
-      </c>
-      <c r="Z10">
-        <v>17</v>
-      </c>
-      <c r="AA10">
-        <v>9</v>
-      </c>
-      <c r="AB10">
-        <f t="shared" si="10"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:28" x14ac:dyDescent="0.3">
+        <v>638</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A11" s="8" t="s">
         <v>60</v>
       </c>
@@ -2678,45 +3321,15 @@
         <v>2024</v>
       </c>
       <c r="N11" s="12">
-        <f t="shared" si="3"/>
+        <f>DATE(L11,J11,K11)</f>
         <v>45480</v>
       </c>
       <c r="R11">
         <f t="shared" ca="1" si="4"/>
-        <v>615</v>
-      </c>
-      <c r="T11">
-        <f t="shared" si="5"/>
-        <v>14</v>
-      </c>
-      <c r="U11">
-        <f t="shared" si="6"/>
-        <v>35</v>
-      </c>
-      <c r="V11">
-        <f t="shared" si="7"/>
-        <v>36</v>
-      </c>
-      <c r="X11" s="13">
-        <f t="shared" si="8"/>
-        <v>0.60805555555555557</v>
-      </c>
-      <c r="Y11" t="str">
-        <f t="shared" si="9"/>
-        <v>02:35 PM</v>
-      </c>
-      <c r="Z11">
-        <v>14</v>
-      </c>
-      <c r="AA11">
-        <v>10</v>
-      </c>
-      <c r="AB11">
-        <f t="shared" si="10"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:28" x14ac:dyDescent="0.3">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A12" s="8" t="s">
         <v>65</v>
       </c>
@@ -2759,40 +3372,10 @@
       </c>
       <c r="R12">
         <f t="shared" ca="1" si="4"/>
-        <v>640</v>
-      </c>
-      <c r="T12">
-        <f t="shared" si="5"/>
-        <v>6</v>
-      </c>
-      <c r="U12">
-        <f t="shared" si="6"/>
-        <v>50</v>
-      </c>
-      <c r="V12">
-        <f t="shared" si="7"/>
-        <v>18</v>
-      </c>
-      <c r="X12" s="13">
-        <f t="shared" si="8"/>
-        <v>0.28493055555555558</v>
-      </c>
-      <c r="Y12" t="str">
-        <f t="shared" si="9"/>
-        <v>06:50 AM</v>
-      </c>
-      <c r="Z12">
-        <v>6</v>
-      </c>
-      <c r="AA12">
-        <v>11</v>
-      </c>
-      <c r="AB12">
-        <f t="shared" si="10"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:28" x14ac:dyDescent="0.3">
+        <v>641</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A13" s="8" t="s">
         <v>70</v>
       </c>
@@ -2835,40 +3418,10 @@
       </c>
       <c r="R13">
         <f t="shared" ca="1" si="4"/>
-        <v>1144</v>
-      </c>
-      <c r="T13">
-        <f t="shared" si="5"/>
-        <v>13</v>
-      </c>
-      <c r="U13">
-        <f t="shared" si="6"/>
-        <v>15</v>
-      </c>
-      <c r="V13">
-        <f t="shared" si="7"/>
-        <v>5</v>
-      </c>
-      <c r="X13" s="13">
-        <f t="shared" si="8"/>
-        <v>0.55214120370370368</v>
-      </c>
-      <c r="Y13" t="str">
-        <f t="shared" si="9"/>
-        <v>01:15 PM</v>
-      </c>
-      <c r="Z13">
-        <v>13</v>
-      </c>
-      <c r="AA13">
-        <v>12</v>
-      </c>
-      <c r="AB13">
-        <f t="shared" si="10"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:28" x14ac:dyDescent="0.3">
+        <v>1145</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A14" s="8" t="s">
         <v>75</v>
       </c>
@@ -2911,40 +3464,10 @@
       </c>
       <c r="R14">
         <f t="shared" ca="1" si="4"/>
-        <v>1093</v>
-      </c>
-      <c r="T14">
-        <f t="shared" si="5"/>
-        <v>11</v>
-      </c>
-      <c r="U14">
-        <f t="shared" si="6"/>
-        <v>45</v>
-      </c>
-      <c r="V14">
-        <f t="shared" si="7"/>
-        <v>39</v>
-      </c>
-      <c r="X14" s="13">
-        <f t="shared" si="8"/>
-        <v>0.49003472222222222</v>
-      </c>
-      <c r="Y14" t="str">
-        <f t="shared" si="9"/>
-        <v>11:45 AM</v>
-      </c>
-      <c r="Z14">
-        <v>11</v>
-      </c>
-      <c r="AA14">
-        <v>13</v>
-      </c>
-      <c r="AB14">
-        <f t="shared" si="10"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:28" x14ac:dyDescent="0.3">
+        <v>1094</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A15" s="8" t="s">
         <v>76</v>
       </c>
@@ -2987,40 +3510,10 @@
       </c>
       <c r="R15">
         <f t="shared" ca="1" si="4"/>
-        <v>1017</v>
-      </c>
-      <c r="T15">
-        <f t="shared" si="5"/>
-        <v>10</v>
-      </c>
-      <c r="U15">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="V15">
-        <f t="shared" si="7"/>
-        <v>51</v>
-      </c>
-      <c r="X15" s="13">
-        <f t="shared" si="8"/>
-        <v>0.41725694444444444</v>
-      </c>
-      <c r="Y15" t="str">
-        <f t="shared" si="9"/>
-        <v>10:00 AM</v>
-      </c>
-      <c r="Z15">
-        <v>10</v>
-      </c>
-      <c r="AA15">
-        <v>14</v>
-      </c>
-      <c r="AB15">
-        <f t="shared" si="10"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:28" x14ac:dyDescent="0.3">
+        <v>1018</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A16" s="8" t="s">
         <v>80</v>
       </c>
@@ -3063,40 +3556,10 @@
       </c>
       <c r="R16">
         <f t="shared" ca="1" si="4"/>
-        <v>927</v>
-      </c>
-      <c r="T16">
-        <f t="shared" si="5"/>
-        <v>17</v>
-      </c>
-      <c r="U16">
-        <f t="shared" si="6"/>
-        <v>30</v>
-      </c>
-      <c r="V16">
-        <f t="shared" si="7"/>
-        <v>14</v>
-      </c>
-      <c r="X16" s="13">
-        <f t="shared" si="8"/>
-        <v>0.72932870370370373</v>
-      </c>
-      <c r="Y16" t="str">
-        <f t="shared" si="9"/>
-        <v>05:30 PM</v>
-      </c>
-      <c r="Z16">
-        <v>17</v>
-      </c>
-      <c r="AA16">
-        <v>15</v>
-      </c>
-      <c r="AB16">
-        <f t="shared" si="10"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:28" x14ac:dyDescent="0.3">
+        <v>928</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A17" s="8" t="s">
         <v>85</v>
       </c>
@@ -3139,40 +3602,10 @@
       </c>
       <c r="R17">
         <f t="shared" ca="1" si="4"/>
-        <v>877</v>
-      </c>
-      <c r="T17">
-        <f t="shared" si="5"/>
-        <v>7</v>
-      </c>
-      <c r="U17">
-        <f t="shared" si="6"/>
-        <v>40</v>
-      </c>
-      <c r="V17">
-        <f t="shared" si="7"/>
-        <v>29</v>
-      </c>
-      <c r="X17" s="13">
-        <f t="shared" si="8"/>
-        <v>0.3197800925925926</v>
-      </c>
-      <c r="Y17" t="str">
-        <f t="shared" si="9"/>
-        <v>07:40 AM</v>
-      </c>
-      <c r="Z17">
-        <v>7</v>
-      </c>
-      <c r="AA17">
-        <v>16</v>
-      </c>
-      <c r="AB17">
-        <f t="shared" si="10"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:28" x14ac:dyDescent="0.3">
+        <v>878</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A18" s="8" t="s">
         <v>87</v>
       </c>
@@ -3215,40 +3648,10 @@
       </c>
       <c r="R18">
         <f t="shared" ca="1" si="4"/>
-        <v>745</v>
-      </c>
-      <c r="T18">
-        <f t="shared" si="5"/>
-        <v>17</v>
-      </c>
-      <c r="U18">
-        <f t="shared" si="6"/>
-        <v>15</v>
-      </c>
-      <c r="V18">
-        <f t="shared" si="7"/>
-        <v>42</v>
-      </c>
-      <c r="X18" s="13">
-        <f t="shared" si="8"/>
-        <v>0.71923611111111108</v>
-      </c>
-      <c r="Y18" t="str">
-        <f t="shared" si="9"/>
-        <v>05:15 PM</v>
-      </c>
-      <c r="Z18">
-        <v>17</v>
-      </c>
-      <c r="AA18">
-        <v>17</v>
-      </c>
-      <c r="AB18">
-        <f t="shared" si="10"/>
-        <v>7</v>
-      </c>
-    </row>
-    <row r="19" spans="1:28" x14ac:dyDescent="0.3">
+        <v>746</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A19" s="8" t="s">
         <v>88</v>
       </c>
@@ -3291,40 +3694,10 @@
       </c>
       <c r="R19">
         <f t="shared" ca="1" si="4"/>
-        <v>677</v>
-      </c>
-      <c r="T19">
-        <f t="shared" si="5"/>
-        <v>17</v>
-      </c>
-      <c r="U19">
-        <f t="shared" si="6"/>
-        <v>25</v>
-      </c>
-      <c r="V19">
-        <f t="shared" si="7"/>
-        <v>57</v>
-      </c>
-      <c r="X19" s="13">
-        <f t="shared" si="8"/>
-        <v>0.72635416666666663</v>
-      </c>
-      <c r="Y19" t="str">
-        <f t="shared" si="9"/>
-        <v>05:25 PM</v>
-      </c>
-      <c r="Z19">
-        <v>17</v>
-      </c>
-      <c r="AA19">
-        <v>18</v>
-      </c>
-      <c r="AB19">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:28" x14ac:dyDescent="0.3">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A20" s="8" t="s">
         <v>93</v>
       </c>
@@ -3367,40 +3740,10 @@
       </c>
       <c r="R20">
         <f t="shared" ca="1" si="4"/>
-        <v>599</v>
-      </c>
-      <c r="T20">
-        <f t="shared" si="5"/>
-        <v>7</v>
-      </c>
-      <c r="U20">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="V20">
-        <f t="shared" si="7"/>
-        <v>3</v>
-      </c>
-      <c r="X20" s="13">
-        <f t="shared" si="8"/>
-        <v>0.29170138888888891</v>
-      </c>
-      <c r="Y20" t="str">
-        <f t="shared" si="9"/>
-        <v>07:00 AM</v>
-      </c>
-      <c r="Z20">
-        <v>7</v>
-      </c>
-      <c r="AA20">
-        <v>19</v>
-      </c>
-      <c r="AB20">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:28" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21" s="8" t="s">
         <v>94</v>
       </c>
@@ -3443,61 +3786,1185 @@
       </c>
       <c r="R21">
         <f t="shared" ca="1" si="4"/>
-        <v>673</v>
-      </c>
-      <c r="T21">
-        <f t="shared" si="5"/>
-        <v>17</v>
-      </c>
-      <c r="U21">
-        <f t="shared" si="6"/>
-        <v>45</v>
-      </c>
-      <c r="V21">
-        <f t="shared" si="7"/>
-        <v>26</v>
-      </c>
-      <c r="X21" s="13">
-        <f t="shared" si="8"/>
-        <v>0.73988425925925927</v>
-      </c>
-      <c r="Y21" t="str">
-        <f t="shared" si="9"/>
-        <v>05:45 PM</v>
-      </c>
-      <c r="Z21">
-        <v>17</v>
-      </c>
-      <c r="AA21">
-        <v>20</v>
-      </c>
-      <c r="AB21">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="AA22">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="23" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="AA23">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="24" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="AA24">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="25" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="AA25">
-        <v>24</v>
+        <v>674</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{98E3AADB-57A3-44C9-A827-28462AE909F4}">
+  <dimension ref="A1:R26"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.21875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="23" customWidth="1"/>
+    <col min="5" max="5" width="29.88671875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="22" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="40" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="2.77734375" customWidth="1"/>
+    <col min="14" max="14" width="15.88671875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.44140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="K1" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="L1" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="N1" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="O1" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q1" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="R1" s="7"/>
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A2" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="D2" s="10">
+        <v>44971.640451388892</v>
+      </c>
+      <c r="E2" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="F2" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="G2" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="H2" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="J2">
+        <f>HOUR(D2)</f>
+        <v>15</v>
+      </c>
+      <c r="K2">
+        <f>MINUTE(D2)</f>
+        <v>22</v>
+      </c>
+      <c r="L2">
+        <f>SECOND(D2)</f>
+        <v>15</v>
+      </c>
+      <c r="N2" s="13">
+        <f>TIME(J2,K2,L2)</f>
+        <v>0.64045138888888886</v>
+      </c>
+      <c r="O2" t="str">
+        <f>TEXT(D2, "hh:mm")</f>
+        <v>15:22</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>14</v>
+      </c>
+      <c r="R2" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A3" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="D3" s="10">
+        <v>45055.40662037037</v>
+      </c>
+      <c r="E3" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="F3" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G3" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="H3" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="J3">
+        <f t="shared" ref="J3:J21" si="0">HOUR(D3)</f>
+        <v>9</v>
+      </c>
+      <c r="K3">
+        <f t="shared" ref="K3:K21" si="1">MINUTE(D3)</f>
+        <v>45</v>
+      </c>
+      <c r="L3">
+        <f t="shared" ref="L3:L21" si="2">SECOND(D3)</f>
+        <v>32</v>
+      </c>
+      <c r="N3" s="13">
+        <f t="shared" ref="N3:N21" si="3">TIME(J3,K3,L3)</f>
+        <v>0.40662037037037035</v>
+      </c>
+      <c r="O3" t="str">
+        <f t="shared" ref="O3:O21" si="4">TEXT(D3, "hh:mm")</f>
+        <v>09:45</v>
+      </c>
+      <c r="Q3" s="17">
+        <v>1</v>
+      </c>
+      <c r="R3">
+        <f>COUNTIF($J$2:$J$21,Q3)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A4" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="D4" s="10">
+        <v>45128.729710648149</v>
+      </c>
+      <c r="E4" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="F4" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="G4" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="H4" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="J4">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="K4">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+      <c r="L4">
+        <f t="shared" si="2"/>
+        <v>47</v>
+      </c>
+      <c r="N4" s="13">
+        <f t="shared" si="3"/>
+        <v>0.72971064814814812</v>
+      </c>
+      <c r="O4" t="str">
+        <f t="shared" si="4"/>
+        <v>17:30</v>
+      </c>
+      <c r="Q4" s="17">
+        <v>2</v>
+      </c>
+      <c r="R4">
+        <f t="shared" ref="R4:R26" si="5">COUNTIF($J$2:$J$21,Q4)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A5" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="D5" s="10">
+        <v>45173.302187499998</v>
+      </c>
+      <c r="E5" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="F5" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="G5" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="H5" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="J5">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="K5">
+        <f t="shared" si="1"/>
+        <v>15</v>
+      </c>
+      <c r="L5">
+        <f t="shared" si="2"/>
+        <v>9</v>
+      </c>
+      <c r="N5" s="13">
+        <f t="shared" si="3"/>
+        <v>0.3021875</v>
+      </c>
+      <c r="O5" t="str">
+        <f t="shared" si="4"/>
+        <v>07:15</v>
+      </c>
+      <c r="Q5" s="17">
+        <v>3</v>
+      </c>
+      <c r="R5">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A6" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="B6" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="D6" s="10">
+        <v>45248.70857638889</v>
+      </c>
+      <c r="E6" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="F6" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="G6" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="H6" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="J6">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="K6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L6">
+        <f t="shared" si="2"/>
+        <v>21</v>
+      </c>
+      <c r="N6" s="13">
+        <f t="shared" si="3"/>
+        <v>0.70857638888888885</v>
+      </c>
+      <c r="O6" t="str">
+        <f t="shared" si="4"/>
+        <v>17:00</v>
+      </c>
+      <c r="Q6" s="17">
+        <v>4</v>
+      </c>
+      <c r="R6">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A7" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="D7" s="10">
+        <v>45302.531921296293</v>
+      </c>
+      <c r="E7" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="F7" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="G7" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="H7" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="J7">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="K7">
+        <f t="shared" si="1"/>
+        <v>45</v>
+      </c>
+      <c r="L7">
+        <f t="shared" si="2"/>
+        <v>58</v>
+      </c>
+      <c r="N7" s="13">
+        <f t="shared" si="3"/>
+        <v>0.53192129629629625</v>
+      </c>
+      <c r="O7" t="str">
+        <f t="shared" si="4"/>
+        <v>12:45</v>
+      </c>
+      <c r="Q7" s="17">
+        <v>5</v>
+      </c>
+      <c r="R7">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A8" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="B8" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="D8" s="10">
+        <v>45354.687881944446</v>
+      </c>
+      <c r="E8" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="F8" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="G8" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="H8" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="J8">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="K8">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+      <c r="L8">
+        <f t="shared" si="2"/>
+        <v>33</v>
+      </c>
+      <c r="N8" s="13">
+        <f t="shared" si="3"/>
+        <v>0.68788194444444439</v>
+      </c>
+      <c r="O8" t="str">
+        <f t="shared" si="4"/>
+        <v>16:30</v>
+      </c>
+      <c r="Q8" s="17">
+        <v>6</v>
+      </c>
+      <c r="R8">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A9" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="B9" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="D9" s="10">
+        <v>45408.340810185182</v>
+      </c>
+      <c r="E9" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="F9" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="G9" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="H9" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="J9">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="K9">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="L9">
+        <f t="shared" si="2"/>
+        <v>46</v>
+      </c>
+      <c r="N9" s="13">
+        <f t="shared" si="3"/>
+        <v>0.34081018518518519</v>
+      </c>
+      <c r="O9" t="str">
+        <f t="shared" si="4"/>
+        <v>08:10</v>
+      </c>
+      <c r="Q9" s="17">
+        <v>7</v>
+      </c>
+      <c r="R9">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A10" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="B10" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="C10" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="D10" s="10">
+        <v>45458.743333333332</v>
+      </c>
+      <c r="E10" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="F10" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="G10" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="H10" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="J10">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="K10">
+        <f t="shared" si="1"/>
+        <v>50</v>
+      </c>
+      <c r="L10">
+        <f t="shared" si="2"/>
+        <v>24</v>
+      </c>
+      <c r="N10" s="13">
+        <f t="shared" si="3"/>
+        <v>0.74333333333333329</v>
+      </c>
+      <c r="O10" t="str">
+        <f t="shared" si="4"/>
+        <v>17:50</v>
+      </c>
+      <c r="Q10" s="17">
+        <v>8</v>
+      </c>
+      <c r="R10">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A11" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="B11" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="C11" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="D11" s="10">
+        <v>45480.608055555553</v>
+      </c>
+      <c r="E11" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="F11" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="G11" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="H11" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="J11">
+        <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="K11">
+        <f t="shared" si="1"/>
+        <v>35</v>
+      </c>
+      <c r="L11">
+        <f t="shared" si="2"/>
+        <v>36</v>
+      </c>
+      <c r="N11" s="13">
+        <f t="shared" si="3"/>
+        <v>0.60805555555555557</v>
+      </c>
+      <c r="O11" t="str">
+        <f t="shared" si="4"/>
+        <v>14:35</v>
+      </c>
+      <c r="Q11" s="17">
+        <v>9</v>
+      </c>
+      <c r="R11">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A12" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="B12" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="C12" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="D12" s="10">
+        <v>45455.284930555557</v>
+      </c>
+      <c r="E12" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="F12" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="G12" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="H12" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="J12">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="K12">
+        <f t="shared" si="1"/>
+        <v>50</v>
+      </c>
+      <c r="L12">
+        <f t="shared" si="2"/>
+        <v>18</v>
+      </c>
+      <c r="N12" s="13">
+        <f t="shared" si="3"/>
+        <v>0.28493055555555558</v>
+      </c>
+      <c r="O12" t="str">
+        <f t="shared" si="4"/>
+        <v>06:50</v>
+      </c>
+      <c r="Q12" s="17">
+        <v>10</v>
+      </c>
+      <c r="R12">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A13" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="B13" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="C13" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="D13" s="10">
+        <v>44951.552141203705</v>
+      </c>
+      <c r="E13" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="F13" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="G13" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="H13" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="J13">
+        <f t="shared" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="K13">
+        <f t="shared" si="1"/>
+        <v>15</v>
+      </c>
+      <c r="L13">
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
+      <c r="N13" s="13">
+        <f t="shared" si="3"/>
+        <v>0.55214120370370368</v>
+      </c>
+      <c r="O13" t="str">
+        <f t="shared" si="4"/>
+        <v>13:15</v>
+      </c>
+      <c r="Q13" s="17">
+        <v>11</v>
+      </c>
+      <c r="R13">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A14" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="B14" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="C14" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="D14" s="10">
+        <v>45002.490034722221</v>
+      </c>
+      <c r="E14" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="F14" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="G14" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="H14" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="J14">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="K14">
+        <f t="shared" si="1"/>
+        <v>45</v>
+      </c>
+      <c r="L14">
+        <f t="shared" si="2"/>
+        <v>39</v>
+      </c>
+      <c r="N14" s="13">
+        <f t="shared" si="3"/>
+        <v>0.49003472222222222</v>
+      </c>
+      <c r="O14" t="str">
+        <f t="shared" si="4"/>
+        <v>11:45</v>
+      </c>
+      <c r="Q14" s="17">
+        <v>12</v>
+      </c>
+      <c r="R14">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A15" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="B15" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="C15" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="D15" s="10">
+        <v>45078.417256944442</v>
+      </c>
+      <c r="E15" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="F15" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="G15" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="H15" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="J15">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="K15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L15">
+        <f t="shared" si="2"/>
+        <v>51</v>
+      </c>
+      <c r="N15" s="13">
+        <f t="shared" si="3"/>
+        <v>0.41725694444444444</v>
+      </c>
+      <c r="O15" t="str">
+        <f t="shared" si="4"/>
+        <v>10:00</v>
+      </c>
+      <c r="Q15" s="17">
+        <v>13</v>
+      </c>
+      <c r="R15">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A16" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="B16" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="C16" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="D16" s="10">
+        <v>45168.729328703703</v>
+      </c>
+      <c r="E16" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="F16" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="G16" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="H16" s="11" t="s">
+        <v>84</v>
+      </c>
+      <c r="J16">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="K16">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+      <c r="L16">
+        <f t="shared" si="2"/>
+        <v>14</v>
+      </c>
+      <c r="N16" s="13">
+        <f t="shared" si="3"/>
+        <v>0.72932870370370373</v>
+      </c>
+      <c r="O16" t="str">
+        <f t="shared" si="4"/>
+        <v>17:30</v>
+      </c>
+      <c r="Q16" s="17">
+        <v>14</v>
+      </c>
+      <c r="R16">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A17" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="B17" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C17" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="D17" s="10">
+        <v>45218.319780092592</v>
+      </c>
+      <c r="E17" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="F17" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G17" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="H17" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="J17">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="K17">
+        <f t="shared" si="1"/>
+        <v>40</v>
+      </c>
+      <c r="L17">
+        <f t="shared" si="2"/>
+        <v>29</v>
+      </c>
+      <c r="N17" s="13">
+        <f t="shared" si="3"/>
+        <v>0.3197800925925926</v>
+      </c>
+      <c r="O17" t="str">
+        <f t="shared" si="4"/>
+        <v>07:40</v>
+      </c>
+      <c r="Q17" s="17">
+        <v>15</v>
+      </c>
+      <c r="R17">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A18" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="B18" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="C18" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="D18" s="10">
+        <v>45350.719236111108</v>
+      </c>
+      <c r="E18" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="F18" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="G18" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="H18" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="J18">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="K18">
+        <f t="shared" si="1"/>
+        <v>15</v>
+      </c>
+      <c r="L18">
+        <f t="shared" si="2"/>
+        <v>42</v>
+      </c>
+      <c r="N18" s="13">
+        <f t="shared" si="3"/>
+        <v>0.71923611111111108</v>
+      </c>
+      <c r="O18" t="str">
+        <f t="shared" si="4"/>
+        <v>17:15</v>
+      </c>
+      <c r="Q18" s="17">
+        <v>16</v>
+      </c>
+      <c r="R18">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A19" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="B19" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="C19" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="D19" s="10">
+        <v>45418.726354166669</v>
+      </c>
+      <c r="E19" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="F19" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="G19" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="H19" s="11" t="s">
+        <v>92</v>
+      </c>
+      <c r="J19">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="K19">
+        <f t="shared" si="1"/>
+        <v>25</v>
+      </c>
+      <c r="L19">
+        <f t="shared" si="2"/>
+        <v>57</v>
+      </c>
+      <c r="N19" s="13">
+        <f t="shared" si="3"/>
+        <v>0.72635416666666663</v>
+      </c>
+      <c r="O19" t="str">
+        <f t="shared" si="4"/>
+        <v>17:25</v>
+      </c>
+      <c r="Q19" s="17">
+        <v>17</v>
+      </c>
+      <c r="R19">
+        <f t="shared" si="5"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A20" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="B20" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="C20" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="D20" s="10">
+        <v>45496.291701388887</v>
+      </c>
+      <c r="E20" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="F20" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="G20" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="H20" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="J20">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="K20">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L20">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="N20" s="13">
+        <f t="shared" si="3"/>
+        <v>0.29170138888888891</v>
+      </c>
+      <c r="O20" t="str">
+        <f t="shared" si="4"/>
+        <v>07:00</v>
+      </c>
+      <c r="Q20" s="17">
+        <v>18</v>
+      </c>
+      <c r="R20">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="B21" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="C21" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="D21" s="15">
+        <v>45422.739884259259</v>
+      </c>
+      <c r="E21" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="F21" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="G21" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="H21" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="J21">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="K21">
+        <f t="shared" si="1"/>
+        <v>45</v>
+      </c>
+      <c r="L21">
+        <f t="shared" si="2"/>
+        <v>26</v>
+      </c>
+      <c r="N21" s="13">
+        <f t="shared" si="3"/>
+        <v>0.73988425925925927</v>
+      </c>
+      <c r="O21" t="str">
+        <f t="shared" si="4"/>
+        <v>17:45</v>
+      </c>
+      <c r="Q21" s="17">
+        <v>19</v>
+      </c>
+      <c r="R21">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="Q22" s="17">
+        <v>20</v>
+      </c>
+      <c r="R22">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="Q23" s="17">
+        <v>21</v>
+      </c>
+      <c r="R23">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="Q24" s="17">
+        <v>22</v>
+      </c>
+      <c r="R24">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="Q25" s="17">
+        <v>23</v>
+      </c>
+      <c r="R25">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="Q26" s="17">
+        <v>24</v>
+      </c>
+      <c r="R26">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:H21" xr:uid="{6C5E2CB8-8C8C-43FB-95B8-5A63A3C08A07}"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>